--- a/data/OutstandingPenalties.xlsx
+++ b/data/OutstandingPenalties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_48598EE7D373ACBFEC5DDC5759F1563A6D80F02D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B34969B-BD85-4CC5-AA5F-892ED0354419}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_48598EE7D373ACBFEC5DDC5759F1563A6D80F02D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590B0D24-894A-4CFC-9FAA-4CD044FD78F2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OutstandingPenalties" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>Driver</t>
   </si>
@@ -91,22 +91,28 @@
     <t>Grid Penalty</t>
   </si>
   <si>
-    <t>Outstanding</t>
-  </si>
-  <si>
-    <t>2024-12-08</t>
-  </si>
-  <si>
     <t>Causing a Collision</t>
   </si>
   <si>
     <t>Collision w/ Kevin Magnussen</t>
+  </si>
+  <si>
+    <t>Void</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Voided by FIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -159,12 +165,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -180,6 +187,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,7 +570,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>21</v>
@@ -568,18 +579,28 @@
         <v>5</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>46086</v>
       </c>
     </row>
   </sheetData>
